--- a/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_dPdt_0_00563.xlsx
+++ b/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_dPdt_0_00563.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E09E16F-32A7-4B97-B429-9CB4DAE585B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A59C0E0-43DB-42D5-896F-ECC9F04282E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -361,82 +361,82 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.48600435256958008</c:v>
+                  <c:v>0.47701683640480042</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.62562930583953857</c:v>
+                  <c:v>0.63989967107772827</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.86731117963790894</c:v>
+                  <c:v>0.88224148750305176</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.163770437240601</c:v>
+                  <c:v>1.192563414573669</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.5670720338821409</c:v>
+                  <c:v>1.562293648719788</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.03956127166748</c:v>
+                  <c:v>2.0404472351074219</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.614729642868042</c:v>
+                  <c:v>2.588354110717773</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.2470376491546631</c:v>
+                  <c:v>3.2453141212463379</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.8701612949371338</c:v>
+                  <c:v>3.88322925567627</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.7408404350280762</c:v>
+                  <c:v>4.6962180137634277</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.4986529350280762</c:v>
+                  <c:v>5.4587807655334473</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.2792506217956543</c:v>
+                  <c:v>6.2970833778381348</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.1685476303100586</c:v>
+                  <c:v>7.0928831100463867</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8.052159309387207</c:v>
+                  <c:v>8.1897363662719727</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.1165533065795898</c:v>
+                  <c:v>9.0614185333251953</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>10.040107727050779</c:v>
+                  <c:v>9.8449068069458008</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>10.83440494537354</c:v>
+                  <c:v>10.942995071411129</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11.755471229553221</c:v>
+                  <c:v>11.755501747131349</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>12.547764778137211</c:v>
+                  <c:v>12.36451435089111</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>13.01962375640869</c:v>
+                  <c:v>12.94475841522217</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>13.344607353210449</c:v>
+                  <c:v>13.556490898132321</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>13.52414035797119</c:v>
+                  <c:v>13.721915245056151</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>13.97608470916748</c:v>
+                  <c:v>13.910262107849119</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>14.289241790771481</c:v>
+                  <c:v>14.100814819335939</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>14.38747596740723</c:v>
+                  <c:v>14.497646331787109</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>14.61384296417236</c:v>
+                  <c:v>14.47349262237549</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -891,82 +891,82 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>6.4385676383972168</c:v>
+                  <c:v>6.4450860023498544</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.0665407180786133</c:v>
+                  <c:v>7.0800962448120117</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.4544219970703116</c:v>
+                  <c:v>7.4762258529663086</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.7110724449157706</c:v>
+                  <c:v>7.7143468856811523</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.8743610382080078</c:v>
+                  <c:v>7.8619484901428223</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.9925532341003418</c:v>
+                  <c:v>7.9865303039550781</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.0889749526977539</c:v>
+                  <c:v>8.0717964172363281</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.1499748229980469</c:v>
+                  <c:v>8.1598148345947266</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.1894721984863281</c:v>
+                  <c:v>8.1949796676635742</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.1996402740478516</c:v>
+                  <c:v>8.222015380859375</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.2290172576904297</c:v>
+                  <c:v>8.23388671875</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.2378997802734375</c:v>
+                  <c:v>8.2485446929931641</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.1751737594604492</c:v>
+                  <c:v>8.1369113922119141</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8.0386428833007813</c:v>
+                  <c:v>8.0501384735107422</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.9423732757568359</c:v>
+                  <c:v>7.9824638366699219</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>7.8649992942810059</c:v>
+                  <c:v>7.8623008728027344</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.7755188941955566</c:v>
+                  <c:v>7.7301936149597168</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.603111743927002</c:v>
+                  <c:v>7.5804123878479004</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7.4859533309936523</c:v>
+                  <c:v>7.518977165222168</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.4043960571289063</c:v>
+                  <c:v>7.3881616592407227</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7.4145078659057617</c:v>
+                  <c:v>7.3272228240966797</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>7.2955155372619629</c:v>
+                  <c:v>7.2820234298706046</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>7.2399883270263672</c:v>
+                  <c:v>7.2510123252868652</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.1858539581298828</c:v>
+                  <c:v>7.1902055740356454</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.212120532989502</c:v>
+                  <c:v>7.139988899230957</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7.1457734107971191</c:v>
+                  <c:v>7.1194419860839844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1418,79 +1418,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>2.7924990281462669E-3</c:v>
+                  <c:v>3.2576567027717829E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.8336372710764408E-3</c:v>
+                  <c:v>4.8468364402651787E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.929185077548027E-3</c:v>
+                  <c:v>6.2064384110271931E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.0660320818424225E-3</c:v>
+                  <c:v>7.3946048505604267E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.4497846439480782E-3</c:v>
+                  <c:v>9.5630716532468796E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.150336768478155E-2</c:v>
+                  <c:v>1.0958137921988961E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.2646160088479521E-2</c:v>
+                  <c:v>1.3139200396835801E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.2462472543120381E-2</c:v>
+                  <c:v>1.275830250233412E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.7413582652807239E-2</c:v>
+                  <c:v>1.625977456569672E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.5156250447034839E-2</c:v>
+                  <c:v>1.5251254662871361E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.561195403337479E-2</c:v>
+                  <c:v>1.6766052693128589E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.7785940319299701E-2</c:v>
+                  <c:v>1.5915995463728901E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.7672233283519741E-2</c:v>
+                  <c:v>2.1937064826488491E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.1287880837917331E-2</c:v>
+                  <c:v>1.743364334106445E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.847108826041222E-2</c:v>
+                  <c:v>1.5669764950871471E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.5885943546891209E-2</c:v>
+                  <c:v>2.196176536381245E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.8421325832605358E-2</c:v>
+                  <c:v>1.62501335144043E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.5845870599150661E-2</c:v>
+                  <c:v>1.218025200068951E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9.4371791929006577E-3</c:v>
+                  <c:v>1.160488091409206E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6.4996718429028988E-3</c:v>
+                  <c:v>1.223464962095022E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.5906601697206502E-3</c:v>
+                  <c:v>3.3084868919104342E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.0388869866728783E-3</c:v>
+                  <c:v>3.766937181353569E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.2631415203213692E-3</c:v>
+                  <c:v>3.8110541645437479E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.9646836444735531E-3</c:v>
+                  <c:v>7.9366303980350494E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.5273397117853156E-3</c:v>
+                  <c:v>-4.830741963814944E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1929,79 +1929,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>1.255946140736341E-2</c:v>
+                  <c:v>1.270020473748446E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.7576255425810814E-3</c:v>
+                  <c:v>7.9225925728678703E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.1330090500414371E-3</c:v>
+                  <c:v>4.7624204307794571E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.2657717820256948E-3</c:v>
+                  <c:v>2.9520320240408182E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.3638438433408742E-3</c:v>
+                  <c:v>2.4916362017393108E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.928434357978404E-3</c:v>
+                  <c:v>1.7053222982212899E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.2199974153190849E-3</c:v>
+                  <c:v>1.7603683518245821E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.8994751675054431E-4</c:v>
+                  <c:v>7.0329668233171105E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.0336151646915821E-4</c:v>
+                  <c:v>5.4071424528956413E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.8753968914970756E-4</c:v>
+                  <c:v>2.374267642153427E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.77650450496003E-4</c:v>
+                  <c:v>2.9315947904251521E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1.2545203790068631E-3</c:v>
+                  <c:v>-2.232666127383709E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2.7306175325065851E-3</c:v>
+                  <c:v>-1.735458383336663E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1.9253921927884221E-3</c:v>
+                  <c:v>-1.3534927275031809E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1.5474796527996659E-3</c:v>
+                  <c:v>-2.40325927734375E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1.7896080389618869E-3</c:v>
+                  <c:v>-2.6421451475471258E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-3.448142902925611E-3</c:v>
+                  <c:v>-2.9956244397908449E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2.343168249353766E-3</c:v>
+                  <c:v>-1.2287044664844871E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1.631145481951535E-3</c:v>
+                  <c:v>-2.6163100264966488E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.0223617320880291E-4</c:v>
+                  <c:v>-1.2187766842544081E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2.3798465263098478E-3</c:v>
+                  <c:v>-9.0398790780454874E-4</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-1.1105441953986881E-3</c:v>
+                  <c:v>-6.2022206839174032E-4</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-1.082687405869365E-3</c:v>
+                  <c:v>-1.2161349877715111E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.2533147390931845E-4</c:v>
+                  <c:v>-1.0043334914371369E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-1.326942467130721E-3</c:v>
+                  <c:v>-4.1093825711868698E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5808,25 +5808,25 @@
         <v>200</v>
       </c>
       <c r="C2">
-        <v>6.4385676383972168</v>
+        <v>6.4450860023498544</v>
       </c>
       <c r="D2">
-        <v>0.69714009761810303</v>
+        <v>0.69066405296325684</v>
       </c>
       <c r="E2">
-        <v>0.48600435256958008</v>
+        <v>0.47701683640480042</v>
       </c>
       <c r="F2">
-        <v>9.8590496927499771E-3</v>
+        <v>9.7674643620848656E-3</v>
       </c>
       <c r="G2">
         <v>250</v>
       </c>
       <c r="H2">
-        <v>1.255946140736341E-2</v>
+        <v>1.270020473748446E-2</v>
       </c>
       <c r="I2">
-        <v>2.7924990281462669E-3</v>
+        <v>3.2576567027717829E-3</v>
       </c>
       <c r="J2">
         <v>50</v>
@@ -5849,25 +5849,25 @@
         <v>250</v>
       </c>
       <c r="C3">
-        <v>7.0665407180786133</v>
+        <v>7.0800962448120117</v>
       </c>
       <c r="D3">
-        <v>0.79096734523773193</v>
+        <v>0.79993730783462524</v>
       </c>
       <c r="E3">
-        <v>0.62562930583953857</v>
+        <v>0.63989967107772827</v>
       </c>
       <c r="F3">
-        <v>1.118596736341715E-2</v>
+        <v>1.131282187998295E-2</v>
       </c>
       <c r="G3">
         <v>300</v>
       </c>
       <c r="H3">
-        <v>7.7576255425810814E-3</v>
+        <v>7.9225925728678703E-3</v>
       </c>
       <c r="I3">
-        <v>4.8336372710764408E-3</v>
+        <v>4.8468364402651787E-3</v>
       </c>
       <c r="J3">
         <v>50</v>
@@ -5881,25 +5881,25 @@
         <v>300</v>
       </c>
       <c r="C4">
-        <v>7.4544219970703116</v>
+        <v>7.4762258529663086</v>
       </c>
       <c r="D4">
-        <v>0.93129545450210571</v>
+        <v>0.93927711248397827</v>
       </c>
       <c r="E4">
-        <v>0.86731117963790894</v>
+        <v>0.88224148750305176</v>
       </c>
       <c r="F4">
-        <v>1.31705068051815E-2</v>
+        <v>1.328338403254747E-2</v>
       </c>
       <c r="G4">
         <v>350</v>
       </c>
       <c r="H4">
-        <v>5.1330090500414371E-3</v>
+        <v>4.7624204307794571E-3</v>
       </c>
       <c r="I4">
-        <v>5.929185077548027E-3</v>
+        <v>6.2064384110271931E-3</v>
       </c>
       <c r="J4">
         <v>50</v>
@@ -5913,25 +5913,25 @@
         <v>350</v>
       </c>
       <c r="C5">
-        <v>7.7110724449157706</v>
+        <v>7.7143468856811523</v>
       </c>
       <c r="D5">
-        <v>1.0787819623947139</v>
+        <v>1.0920455455780029</v>
       </c>
       <c r="E5">
-        <v>1.163770437240601</v>
+        <v>1.192563414573669</v>
       </c>
       <c r="F5">
-        <v>1.5256281010806561E-2</v>
+        <v>1.544385589659214E-2</v>
       </c>
       <c r="G5">
         <v>400</v>
       </c>
       <c r="H5">
-        <v>3.2657717820256948E-3</v>
+        <v>2.9520320240408182E-3</v>
       </c>
       <c r="I5">
-        <v>8.0660320818424225E-3</v>
+        <v>7.3946048505604267E-3</v>
       </c>
       <c r="J5">
         <v>50</v>
@@ -5945,25 +5945,25 @@
         <v>400</v>
       </c>
       <c r="C6">
-        <v>7.8743610382080078</v>
+        <v>7.8619484901428223</v>
       </c>
       <c r="D6">
-        <v>1.251827478408813</v>
+        <v>1.2499175071716311</v>
       </c>
       <c r="E6">
-        <v>1.5670720338821409</v>
+        <v>1.562293648719788</v>
       </c>
       <c r="F6">
-        <v>1.770351454615593E-2</v>
+        <v>1.7676502466201779E-2</v>
       </c>
       <c r="G6">
         <v>450</v>
       </c>
       <c r="H6">
-        <v>2.3638438433408742E-3</v>
+        <v>2.4916362017393108E-3</v>
       </c>
       <c r="I6">
-        <v>9.4497846439480782E-3</v>
+        <v>9.5630716532468796E-3</v>
       </c>
       <c r="J6">
         <v>50</v>
@@ -5977,25 +5977,25 @@
         <v>450</v>
       </c>
       <c r="C7">
-        <v>7.9925532341003418</v>
+        <v>7.9865303039550781</v>
       </c>
       <c r="D7">
-        <v>1.428132057189941</v>
+        <v>1.428442239761353</v>
       </c>
       <c r="E7">
-        <v>2.03956127166748</v>
+        <v>2.0404472351074219</v>
       </c>
       <c r="F7">
-        <v>2.0196836441755291E-2</v>
+        <v>2.020122297108173E-2</v>
       </c>
       <c r="G7">
         <v>500</v>
       </c>
       <c r="H7">
-        <v>1.928434357978404E-3</v>
+        <v>1.7053222982212899E-3</v>
       </c>
       <c r="I7">
-        <v>1.150336768478155E-2</v>
+        <v>1.0958137921988961E-2</v>
       </c>
       <c r="J7">
         <v>50</v>
@@ -6009,25 +6009,25 @@
         <v>500</v>
       </c>
       <c r="C8">
-        <v>8.0889749526977539</v>
+        <v>8.0717964172363281</v>
       </c>
       <c r="D8">
-        <v>1.617012619972229</v>
+        <v>1.60883629322052</v>
       </c>
       <c r="E8">
-        <v>2.614729642868042</v>
+        <v>2.588354110717773</v>
       </c>
       <c r="F8">
-        <v>2.2868011146783829E-2</v>
+        <v>2.2752381861209869E-2</v>
       </c>
       <c r="G8">
         <v>550</v>
       </c>
       <c r="H8">
-        <v>1.2199974153190849E-3</v>
+        <v>1.7603683518245821E-3</v>
       </c>
       <c r="I8">
-        <v>1.2646160088479521E-2</v>
+        <v>1.3139200396835801E-2</v>
       </c>
       <c r="J8">
         <v>50</v>
@@ -6041,25 +6041,25 @@
         <v>550</v>
       </c>
       <c r="C9">
-        <v>8.1499748229980469</v>
+        <v>8.1598148345947266</v>
       </c>
       <c r="D9">
-        <v>1.801953792572021</v>
+        <v>1.801475524902344</v>
       </c>
       <c r="E9">
-        <v>3.2470376491546631</v>
+        <v>3.2453141212463379</v>
       </c>
       <c r="F9">
-        <v>2.5483474135398861E-2</v>
+        <v>2.5476710870862011E-2</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
-        <v>7.8994751675054431E-4</v>
+        <v>7.0329668233171105E-4</v>
       </c>
       <c r="I9">
-        <v>1.2462472543120381E-2</v>
+        <v>1.275830250233412E-2</v>
       </c>
       <c r="J9">
         <v>50</v>
@@ -6073,25 +6073,25 @@
         <v>600</v>
       </c>
       <c r="C10">
-        <v>8.1894721984863281</v>
+        <v>8.1949796676635742</v>
       </c>
       <c r="D10">
-        <v>1.9672725200653081</v>
+        <v>1.970591068267822</v>
       </c>
       <c r="E10">
-        <v>3.8701612949371338</v>
+        <v>3.88322925567627</v>
       </c>
       <c r="F10">
-        <v>2.7821434661746029E-2</v>
+        <v>2.7868365868926048E-2</v>
       </c>
       <c r="G10">
         <v>650</v>
       </c>
       <c r="H10">
-        <v>2.0336151646915821E-4</v>
+        <v>5.4071424528956413E-4</v>
       </c>
       <c r="I10">
-        <v>1.7413582652807239E-2</v>
+        <v>1.625977456569672E-2</v>
       </c>
       <c r="J10">
         <v>50</v>
@@ -6105,25 +6105,25 @@
         <v>650</v>
       </c>
       <c r="C11">
-        <v>8.1996402740478516</v>
+        <v>8.222015380859375</v>
       </c>
       <c r="D11">
-        <v>2.1773471832275391</v>
+        <v>2.1670758724212651</v>
       </c>
       <c r="E11">
-        <v>4.7408404350280762</v>
+        <v>4.6962180137634277</v>
       </c>
       <c r="F11">
-        <v>3.0792338773608211E-2</v>
+        <v>3.0647080391645432E-2</v>
       </c>
       <c r="G11">
         <v>700</v>
       </c>
       <c r="H11">
-        <v>5.8753968914970756E-4</v>
+        <v>2.374267642153427E-4</v>
       </c>
       <c r="I11">
-        <v>1.5156250447034839E-2</v>
+        <v>1.5251254662871361E-2</v>
       </c>
       <c r="J11">
         <v>50</v>
@@ -6137,25 +6137,25 @@
         <v>700</v>
       </c>
       <c r="C12">
-        <v>8.2290172576904297</v>
+        <v>8.23388671875</v>
       </c>
       <c r="D12">
-        <v>2.3449206352233891</v>
+        <v>2.336403369903564</v>
       </c>
       <c r="E12">
-        <v>5.4986529350280762</v>
+        <v>5.4587807655334473</v>
       </c>
       <c r="F12">
-        <v>3.3162184059619897E-2</v>
+        <v>3.3041734248399728E-2</v>
       </c>
       <c r="G12">
         <v>750</v>
       </c>
       <c r="H12">
-        <v>1.77650450496003E-4</v>
+        <v>2.9315947904251521E-4</v>
       </c>
       <c r="I12">
-        <v>1.561195403337479E-2</v>
+        <v>1.6766052693128589E-2</v>
       </c>
       <c r="J12">
         <v>50</v>
@@ -6169,25 +6169,25 @@
         <v>750</v>
       </c>
       <c r="C13">
-        <v>8.2378997802734375</v>
+        <v>8.2485446929931641</v>
       </c>
       <c r="D13">
-        <v>2.5058434009552002</v>
+        <v>2.5093989372253418</v>
       </c>
       <c r="E13">
-        <v>6.2792506217956543</v>
+        <v>6.2970833778381348</v>
       </c>
       <c r="F13">
-        <v>3.5437978804111481E-2</v>
+        <v>3.5488259047269821E-2</v>
       </c>
       <c r="G13">
         <v>800</v>
       </c>
       <c r="H13">
-        <v>-1.2545203790068631E-3</v>
+        <v>-2.232666127383709E-3</v>
       </c>
       <c r="I13">
-        <v>1.7785940319299701E-2</v>
+        <v>1.5915995463728901E-2</v>
       </c>
       <c r="J13">
         <v>50</v>
@@ -6201,25 +6201,25 @@
         <v>800</v>
       </c>
       <c r="C14">
-        <v>8.1751737594604492</v>
+        <v>8.1369113922119141</v>
       </c>
       <c r="D14">
-        <v>2.6774144172668461</v>
+        <v>2.663246631622314</v>
       </c>
       <c r="E14">
-        <v>7.1685476303100586</v>
+        <v>7.0928831100463867</v>
       </c>
       <c r="F14">
-        <v>3.7864357233047492E-2</v>
+        <v>3.766399621963501E-2</v>
       </c>
       <c r="G14">
         <v>850</v>
       </c>
       <c r="H14">
-        <v>-2.7306175325065851E-3</v>
+        <v>-1.735458383336663E-3</v>
       </c>
       <c r="I14">
-        <v>1.7672233283519741E-2</v>
+        <v>2.1937064826488491E-2</v>
       </c>
       <c r="J14">
         <v>50</v>
@@ -6233,25 +6233,25 @@
         <v>850</v>
       </c>
       <c r="C15">
-        <v>8.0386428833007813</v>
+        <v>8.0501384735107422</v>
       </c>
       <c r="D15">
-        <v>2.8376326560974121</v>
+        <v>2.8617715835571289</v>
       </c>
       <c r="E15">
-        <v>8.052159309387207</v>
+        <v>8.1897363662719727</v>
       </c>
       <c r="F15">
-        <v>4.0130186825990677E-2</v>
+        <v>4.0471561253070831E-2</v>
       </c>
       <c r="G15">
         <v>900</v>
       </c>
       <c r="H15">
-        <v>-1.9253921927884221E-3</v>
+        <v>-1.3534927275031809E-3</v>
       </c>
       <c r="I15">
-        <v>2.1287880837917331E-2</v>
+        <v>1.743364334106445E-2</v>
       </c>
       <c r="J15">
         <v>50</v>
@@ -6265,25 +6265,25 @@
         <v>900</v>
       </c>
       <c r="C16">
-        <v>7.9423732757568359</v>
+        <v>7.9824638366699219</v>
       </c>
       <c r="D16">
-        <v>3.019363164901733</v>
+        <v>3.0102190971374512</v>
       </c>
       <c r="E16">
-        <v>9.1165533065795898</v>
+        <v>9.0614185333251953</v>
       </c>
       <c r="F16">
-        <v>4.2700242251157761E-2</v>
+        <v>4.2570926249027252E-2</v>
       </c>
       <c r="G16">
         <v>950</v>
       </c>
       <c r="H16">
-        <v>-1.5474796527996659E-3</v>
+        <v>-2.40325927734375E-3</v>
       </c>
       <c r="I16">
-        <v>1.847108826041222E-2</v>
+        <v>1.5669764950871471E-2</v>
       </c>
       <c r="J16">
         <v>50</v>
@@ -6297,25 +6297,25 @@
         <v>950</v>
       </c>
       <c r="C17">
-        <v>7.8649992942810059</v>
+        <v>7.8623008728027344</v>
       </c>
       <c r="D17">
-        <v>3.168612957000732</v>
+        <v>3.1376595497131352</v>
       </c>
       <c r="E17">
-        <v>10.040107727050779</v>
+        <v>9.8449068069458008</v>
       </c>
       <c r="F17">
-        <v>4.4810954481363303E-2</v>
+        <v>4.4373206794261932E-2</v>
       </c>
       <c r="G17">
         <v>1000</v>
       </c>
       <c r="H17">
-        <v>-1.7896080389618869E-3</v>
+        <v>-2.6421451475471258E-3</v>
       </c>
       <c r="I17">
-        <v>1.5885943546891209E-2</v>
+        <v>2.196176536381245E-2</v>
       </c>
       <c r="J17">
         <v>50</v>
@@ -6329,25 +6329,25 @@
         <v>1000</v>
       </c>
       <c r="C18">
-        <v>7.7755188941955566</v>
+        <v>7.7301936149597168</v>
       </c>
       <c r="D18">
-        <v>3.2915656566619869</v>
+        <v>3.308019876480103</v>
       </c>
       <c r="E18">
-        <v>10.83440494537354</v>
+        <v>10.942995071411129</v>
       </c>
       <c r="F18">
-        <v>4.6549767255783081E-2</v>
+        <v>4.6782467514276498E-2</v>
       </c>
       <c r="G18">
         <v>1050</v>
       </c>
       <c r="H18">
-        <v>-3.448142902925611E-3</v>
+        <v>-2.9956244397908449E-3</v>
       </c>
       <c r="I18">
-        <v>1.8421325832605358E-2</v>
+        <v>1.62501335144043E-2</v>
       </c>
       <c r="J18">
         <v>50</v>
@@ -6361,25 +6361,25 @@
         <v>1050</v>
       </c>
       <c r="C19">
-        <v>7.603111743927002</v>
+        <v>7.5804123878479004</v>
       </c>
       <c r="D19">
-        <v>3.428625345230103</v>
+        <v>3.4286296367645259</v>
       </c>
       <c r="E19">
-        <v>11.755471229553221</v>
+        <v>11.755501747131349</v>
       </c>
       <c r="F19">
-        <v>4.8488084226846688E-2</v>
+        <v>4.848814383149147E-2</v>
       </c>
       <c r="G19">
         <v>1100</v>
       </c>
       <c r="H19">
-        <v>-2.343168249353766E-3</v>
+        <v>-1.2287044664844871E-3</v>
       </c>
       <c r="I19">
-        <v>1.5845870599150661E-2</v>
+        <v>1.218025200068951E-2</v>
       </c>
       <c r="J19">
         <v>50</v>
@@ -6393,25 +6393,25 @@
         <v>1100</v>
       </c>
       <c r="C20">
-        <v>7.4859533309936523</v>
+        <v>7.518977165222168</v>
       </c>
       <c r="D20">
-        <v>3.542282342910767</v>
+        <v>3.516321182250977</v>
       </c>
       <c r="E20">
-        <v>12.547764778137211</v>
+        <v>12.36451435089111</v>
       </c>
       <c r="F20">
-        <v>5.0095438957214362E-2</v>
+        <v>4.9728289246559143E-2</v>
       </c>
       <c r="G20">
         <v>1150</v>
       </c>
       <c r="H20">
-        <v>-1.631145481951535E-3</v>
+        <v>-2.6163100264966488E-3</v>
       </c>
       <c r="I20">
-        <v>9.4371791929006577E-3</v>
+        <v>1.160488091409206E-2</v>
       </c>
       <c r="J20">
         <v>50</v>
@@ -6425,25 +6425,25 @@
         <v>1150</v>
       </c>
       <c r="C21">
-        <v>7.4043960571289063</v>
+        <v>7.3881616592407227</v>
       </c>
       <c r="D21">
-        <v>3.608271598815918</v>
+        <v>3.5978825092315669</v>
       </c>
       <c r="E21">
-        <v>13.01962375640869</v>
+        <v>12.94475841522217</v>
       </c>
       <c r="F21">
-        <v>5.1028665155172348E-2</v>
+        <v>5.0881743431091309E-2</v>
       </c>
       <c r="G21">
         <v>1200</v>
       </c>
       <c r="H21">
-        <v>2.0223617320880291E-4</v>
+        <v>-1.2187766842544081E-3</v>
       </c>
       <c r="I21">
-        <v>6.4996718429028988E-3</v>
+        <v>1.223464962095022E-2</v>
       </c>
       <c r="J21">
         <v>50</v>
@@ -6457,25 +6457,25 @@
         <v>1200</v>
       </c>
       <c r="C22">
-        <v>7.4145078659057617</v>
+        <v>7.3272228240966797</v>
       </c>
       <c r="D22">
-        <v>3.6530270576477051</v>
+        <v>3.681914091110229</v>
       </c>
       <c r="E22">
-        <v>13.344607353210449</v>
+        <v>13.556490898132321</v>
       </c>
       <c r="F22">
-        <v>5.1661603152751923E-2</v>
+        <v>5.2070129662752151E-2</v>
       </c>
       <c r="G22">
         <v>1250</v>
       </c>
       <c r="H22">
-        <v>-2.3798465263098478E-3</v>
+        <v>-9.0398790780454874E-4</v>
       </c>
       <c r="I22">
-        <v>3.5906601697206502E-3</v>
+        <v>3.3084868919104342E-3</v>
       </c>
       <c r="J22">
         <v>50</v>
@@ -6489,25 +6489,25 @@
         <v>1250</v>
       </c>
       <c r="C23">
-        <v>7.2955155372619629</v>
+        <v>7.2820234298706046</v>
       </c>
       <c r="D23">
-        <v>3.6775181293487549</v>
+        <v>3.704310417175293</v>
       </c>
       <c r="E23">
-        <v>13.52414035797119</v>
+        <v>13.721915245056151</v>
       </c>
       <c r="F23">
-        <v>5.2007962018251419E-2</v>
+        <v>5.238686129450798E-2</v>
       </c>
       <c r="G23">
         <v>1300</v>
       </c>
       <c r="H23">
-        <v>-1.1105441953986881E-3</v>
+        <v>-6.2022206839174032E-4</v>
       </c>
       <c r="I23">
-        <v>9.0388869866728783E-3</v>
+        <v>3.766937181353569E-3</v>
       </c>
       <c r="J23">
         <v>50</v>
@@ -6521,25 +6521,25 @@
         <v>1300</v>
       </c>
       <c r="C24">
-        <v>7.2399883270263672</v>
+        <v>7.2510123252868652</v>
       </c>
       <c r="D24">
-        <v>3.7384603023529048</v>
+        <v>3.7296464443206792</v>
       </c>
       <c r="E24">
-        <v>13.97608470916748</v>
+        <v>13.910262107849119</v>
       </c>
       <c r="F24">
-        <v>5.2869811654090881E-2</v>
+        <v>5.2745167165994637E-2</v>
       </c>
       <c r="G24">
         <v>1350</v>
       </c>
       <c r="H24">
-        <v>-1.082687405869365E-3</v>
+        <v>-1.2161349877715111E-3</v>
       </c>
       <c r="I24">
-        <v>6.2631415203213692E-3</v>
+        <v>3.8110541645437479E-3</v>
       </c>
       <c r="J24">
         <v>50</v>
@@ -6553,25 +6553,25 @@
         <v>1350</v>
       </c>
       <c r="C25">
-        <v>7.1858539581298828</v>
+        <v>7.1902055740356454</v>
       </c>
       <c r="D25">
-        <v>3.7801113128662109</v>
+        <v>3.7551052570343022</v>
       </c>
       <c r="E25">
-        <v>14.289241790771481</v>
+        <v>14.100814819335939</v>
       </c>
       <c r="F25">
-        <v>5.3458847105503082E-2</v>
+        <v>5.3105209022760391E-2</v>
       </c>
       <c r="G25">
         <v>1400</v>
       </c>
       <c r="H25">
-        <v>5.2533147390931845E-4</v>
+        <v>-1.0043334914371369E-3</v>
       </c>
       <c r="I25">
-        <v>1.9646836444735531E-3</v>
+        <v>7.9366303980350494E-3</v>
       </c>
       <c r="J25">
         <v>50</v>
@@ -6585,25 +6585,25 @@
         <v>1400</v>
       </c>
       <c r="C26">
-        <v>7.212120532989502</v>
+        <v>7.139988899230957</v>
       </c>
       <c r="D26">
-        <v>3.793082714080811</v>
+        <v>3.80757737159729</v>
       </c>
       <c r="E26">
-        <v>14.38747596740723</v>
+        <v>14.497646331787109</v>
       </c>
       <c r="F26">
-        <v>5.3642291575670242E-2</v>
+        <v>5.3847275674343109E-2</v>
       </c>
       <c r="G26">
         <v>1450</v>
       </c>
       <c r="H26">
-        <v>-1.326942467130721E-3</v>
+        <v>-4.1093825711868698E-4</v>
       </c>
       <c r="I26">
-        <v>4.5273397117853156E-3</v>
+        <v>-4.830741963814944E-4</v>
       </c>
       <c r="J26">
         <v>50</v>
@@ -6617,16 +6617,16 @@
         <v>1450</v>
       </c>
       <c r="C27">
-        <v>7.1457734107971191</v>
+        <v>7.1194419860839844</v>
       </c>
       <c r="D27">
-        <v>3.822805643081665</v>
+        <v>3.8044042587280269</v>
       </c>
       <c r="E27">
-        <v>14.61384296417236</v>
+        <v>14.47349262237549</v>
       </c>
       <c r="F27">
-        <v>5.4062634706497192E-2</v>
+        <v>5.3802400827407837E-2</v>
       </c>
       <c r="G27">
         <v>1450</v>

--- a/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_dPdt_0_00563.xlsx
+++ b/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_dPdt_0_00563.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A59C0E0-43DB-42D5-896F-ECC9F04282E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7548C8AC-767B-4C91-A269-873D393EF515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -269,174 +269,258 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$27</c:f>
+              <c:f>Sheet1!$B$2:$B$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>200</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="7">
                   <c:v>350</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
                   <c:v>400</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>450</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="11">
                   <c:v>550</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="12">
                   <c:v>600</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="13">
                   <c:v>650</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="14">
                   <c:v>700</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="15">
                   <c:v>750</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="16">
                   <c:v>800</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="17">
                   <c:v>850</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="18">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="19">
                   <c:v>950</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="20">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="21">
                   <c:v>1050</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>1100</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>1150</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
                   <c:v>1200</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="25">
                   <c:v>1250</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="26">
                   <c:v>1300</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="27">
                   <c:v>1350</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="28">
                   <c:v>1400</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="29">
                   <c:v>1450</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1550</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1650</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1750</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1850</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1950</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$27</c:f>
+              <c:f>Sheet1!$E$2:$E$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>0.47701683640480042</c:v>
+                  <c:v>0.3056810200214386</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.63989967107772827</c:v>
+                  <c:v>0.29865846037864691</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.88224148750305176</c:v>
+                  <c:v>0.3177030086517334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.192563414573669</c:v>
+                  <c:v>0.38065990805625921</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.562293648719788</c:v>
+                  <c:v>0.48854783177375788</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.0404472351074219</c:v>
+                  <c:v>0.63860732316970825</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.588354110717773</c:v>
+                  <c:v>0.86919867992401123</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.2453141212463379</c:v>
+                  <c:v>1.172087550163269</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.88322925567627</c:v>
+                  <c:v>1.5486912727355959</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.6962180137634277</c:v>
+                  <c:v>2.035842657089233</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.4587807655334473</c:v>
+                  <c:v>2.607041597366333</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.2970833778381348</c:v>
+                  <c:v>3.192379236221313</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.0928831100463867</c:v>
+                  <c:v>3.932708740234375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8.1897363662719727</c:v>
+                  <c:v>4.6872353553771973</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.0614185333251953</c:v>
+                  <c:v>5.3665204048156738</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.8449068069458008</c:v>
+                  <c:v>6.3872747421264648</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>10.942995071411129</c:v>
+                  <c:v>7.1897616386413574</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11.755501747131349</c:v>
+                  <c:v>8.004490852355957</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>12.36451435089111</c:v>
+                  <c:v>9.1572561264038086</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>12.94475841522217</c:v>
+                  <c:v>9.9829435348510742</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>13.556490898132321</c:v>
+                  <c:v>10.88094997406006</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>13.721915245056151</c:v>
+                  <c:v>11.6551628112793</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>13.910262107849119</c:v>
+                  <c:v>12.3659610748291</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>14.100814819335939</c:v>
+                  <c:v>13.001992225646971</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>14.497646331787109</c:v>
+                  <c:v>13.54195022583008</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>14.47349262237549</c:v>
+                  <c:v>13.74445152282715</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>14.13855457305908</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>14.34046745300293</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>14.515537261962891</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>14.631058692932131</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>14.6892147064209</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>14.819558143615721</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>14.88661003112793</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>14.89436054229736</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>15.059609413146971</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>14.94306659698486</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>15.063291549682621</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>14.966390609741209</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>15.0908088684082</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>15.217677116394039</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -799,174 +883,258 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$27</c:f>
+              <c:f>Sheet1!$B$2:$B$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>200</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="7">
                   <c:v>350</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
                   <c:v>400</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>450</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="11">
                   <c:v>550</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="12">
                   <c:v>600</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="13">
                   <c:v>650</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="14">
                   <c:v>700</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="15">
                   <c:v>750</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="16">
                   <c:v>800</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="17">
                   <c:v>850</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="18">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="19">
                   <c:v>950</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="20">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="21">
                   <c:v>1050</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>1100</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>1150</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
                   <c:v>1200</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="25">
                   <c:v>1250</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="26">
                   <c:v>1300</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="27">
                   <c:v>1350</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="28">
                   <c:v>1400</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="29">
                   <c:v>1450</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1550</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1650</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1750</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1850</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1950</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$27</c:f>
+              <c:f>Sheet1!$C$2:$C$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>6.4450860023498544</c:v>
+                  <c:v>-3.3186677843332291E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.0800962448120117</c:v>
+                  <c:v>2.153664112091064</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.4762258529663086</c:v>
+                  <c:v>4.0756592750549316</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.7143468856811523</c:v>
+                  <c:v>5.4786391258239746</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.8619484901428223</c:v>
+                  <c:v>6.4430904388427734</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.9865303039550781</c:v>
+                  <c:v>7.0740365982055664</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.0717964172363281</c:v>
+                  <c:v>7.4741420745849609</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.1598148345947266</c:v>
+                  <c:v>7.707155704498291</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.1949796676635742</c:v>
+                  <c:v>7.8932123184204102</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.222015380859375</c:v>
+                  <c:v>7.9929924011230469</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.23388671875</c:v>
+                  <c:v>8.0965328216552734</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.2485446929931641</c:v>
+                  <c:v>8.12677001953125</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.1369113922119141</c:v>
+                  <c:v>8.1885309219360352</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8.0501384735107422</c:v>
+                  <c:v>8.2121171951293945</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.9824638366699219</c:v>
+                  <c:v>8.2405185699462891</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>7.8623008728027344</c:v>
+                  <c:v>8.1979074478149414</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.7301936149597168</c:v>
+                  <c:v>8.1539754867553711</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.5804123878479004</c:v>
+                  <c:v>8.0933647155761719</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7.518977165222168</c:v>
+                  <c:v>7.9831967353820801</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.3881616592407227</c:v>
+                  <c:v>7.8224811553955078</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7.3272228240966797</c:v>
+                  <c:v>7.7050294876098633</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>7.2820234298706046</c:v>
+                  <c:v>7.6080164909362793</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>7.2510123252868652</c:v>
+                  <c:v>7.506319522857666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.1902055740356454</c:v>
+                  <c:v>7.4146342277526864</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.139988899230957</c:v>
+                  <c:v>7.3405756950378418</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7.1194419860839844</c:v>
+                  <c:v>7.2707390785217294</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.2047357559204102</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7.2338976860046387</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7.1513657569885254</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7.1125006675720206</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7.129849910736084</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7.0729751586914063</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7.1124234199523926</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7.0587763786315918</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7.0713930130004883</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7.0836243629455566</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7.0776844024658203</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7.0861234664916992</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7.0272951126098633</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7.0584759712219238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1306,11 +1474,125 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
+              <c:f>Sheet1!$I$2:$I$40</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>mu</c:v>
+                  <c:v>-0.000140451</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.000380891</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.001259138</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.002157758</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.00300119</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.004611827</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.006057777</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.007532075</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.009743027</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.011423979</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.011706753</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.01480659</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.015090533</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.013585701</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.020415086</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.016049737</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.016294584</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.023055306</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.016513748</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.017960129</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.015484257</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.014215965</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.012720623</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.01079916</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.004050026</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.007882061</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.004038258</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.003501396</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.002310429</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.00116312</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.002606869</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.001341038</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.00015501</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.003304977</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.002330856</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.002404499</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.001938019</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.002488365</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.002537365</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1329,84 +1611,126 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$26</c:f>
+              <c:f>Sheet1!$B$2:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>200</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="7">
                   <c:v>350</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
                   <c:v>400</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>450</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="11">
                   <c:v>550</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="12">
                   <c:v>600</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="13">
                   <c:v>650</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="14">
                   <c:v>700</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="15">
                   <c:v>750</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="16">
                   <c:v>800</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="17">
                   <c:v>850</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="18">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="19">
                   <c:v>950</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="20">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="21">
                   <c:v>1050</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>1100</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>1150</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
                   <c:v>1200</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="25">
                   <c:v>1250</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="26">
                   <c:v>1300</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="27">
                   <c:v>1350</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="28">
                   <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1450</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1550</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1650</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1750</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1850</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1418,79 +1742,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>3.2576567027717829E-3</c:v>
+                  <c:v>-1.4045118587091571E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.8468364402651787E-3</c:v>
+                  <c:v>3.8089096779003739E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.2064384110271931E-3</c:v>
+                  <c:v>1.259137992747128E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.3946048505604267E-3</c:v>
+                  <c:v>2.1577584557235241E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.5630716532468796E-3</c:v>
+                  <c:v>3.0011897906661029E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0958137921988961E-2</c:v>
+                  <c:v>4.6118269674479961E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.3139200396835801E-2</c:v>
+                  <c:v>6.0577774420380592E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.275830250233412E-2</c:v>
+                  <c:v>7.5320745818316936E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.625977456569672E-2</c:v>
+                  <c:v>9.74302738904953E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.5251254662871361E-2</c:v>
+                  <c:v>1.1423978954553601E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.6766052693128589E-2</c:v>
+                  <c:v>1.17067527025938E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.5915995463728901E-2</c:v>
+                  <c:v>1.4806590043008329E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.1937064826488491E-2</c:v>
+                  <c:v>1.5090532600879669E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.743364334106445E-2</c:v>
+                  <c:v>1.3585700653493399E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.5669764950871471E-2</c:v>
+                  <c:v>2.0415086299180981E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.196176536381245E-2</c:v>
+                  <c:v>1.6049737110733989E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.62501335144043E-2</c:v>
+                  <c:v>1.6294583678245541E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.218025200068951E-2</c:v>
+                  <c:v>2.3055305704474449E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.160488091409206E-2</c:v>
+                  <c:v>1.651374809443951E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.223464962095022E-2</c:v>
+                  <c:v>1.7960129305720329E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.3084868919104342E-3</c:v>
+                  <c:v>1.548425666987896E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3.766937181353569E-3</c:v>
+                  <c:v>1.421596482396126E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3.8110541645437479E-3</c:v>
+                  <c:v>1.272062305361032E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.9366303980350494E-3</c:v>
+                  <c:v>1.0799160227179531E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-4.830741963814944E-4</c:v>
+                  <c:v>4.0500257164239883E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1840,168 +2164,252 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$26</c:f>
+              <c:f>Sheet1!$B$2:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>200</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="7">
                   <c:v>350</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
                   <c:v>400</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>450</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="11">
                   <c:v>550</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="12">
                   <c:v>600</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="13">
                   <c:v>650</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="14">
                   <c:v>700</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="15">
                   <c:v>750</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="16">
                   <c:v>800</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="17">
                   <c:v>850</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="18">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="19">
                   <c:v>950</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="20">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="21">
                   <c:v>1050</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>1100</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>1150</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
                   <c:v>1200</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="25">
                   <c:v>1250</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="26">
                   <c:v>1300</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="27">
                   <c:v>1350</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="28">
                   <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1450</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1550</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1650</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1750</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1850</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$2:$H$26</c:f>
+              <c:f>Sheet1!$H$2:$H$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>1.270020473748446E-2</c:v>
+                  <c:v>4.3737016618251801E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.9225925728678703E-3</c:v>
+                  <c:v>3.8439903408288963E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7624204307794571E-3</c:v>
+                  <c:v>2.805959619581699E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.9520320240408182E-3</c:v>
+                  <c:v>1.9289026036858559E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.4916362017393108E-3</c:v>
+                  <c:v>1.2618923559784889E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.7053222982212899E-3</c:v>
+                  <c:v>8.0021098256111145E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.7603683518245821E-3</c:v>
+                  <c:v>4.6602725051343441E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.0329668233171105E-4</c:v>
+                  <c:v>3.7211321759969E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.4071424528956413E-4</c:v>
+                  <c:v>1.9956016913056369E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.374267642153427E-4</c:v>
+                  <c:v>2.0708083175122738E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.9315947904251521E-4</c:v>
+                  <c:v>6.0474395286291838E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2.232666127383709E-3</c:v>
+                  <c:v>1.2352180201560261E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1.735458383336663E-3</c:v>
+                  <c:v>4.7172547783702612E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1.3534927275031809E-3</c:v>
+                  <c:v>5.6802749168127775E-4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-2.40325927734375E-3</c:v>
+                  <c:v>-8.5222243797034025E-4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2.6421451475471258E-3</c:v>
+                  <c:v>-8.7863922817632556E-4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2.9956244397908449E-3</c:v>
+                  <c:v>-1.21221540030092E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1.2287044664844871E-3</c:v>
+                  <c:v>-2.2033595014363532E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2.6163100264966488E-3</c:v>
+                  <c:v>-3.214311553165317E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1.2187766842544081E-3</c:v>
+                  <c:v>-2.349033253267407E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-9.0398790780454874E-4</c:v>
+                  <c:v>-1.940259942784905E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-6.2022206839174032E-4</c:v>
+                  <c:v>-2.0339393522590399E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-1.2161349877715111E-3</c:v>
+                  <c:v>-1.833705930039287E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-1.0043334914371369E-3</c:v>
+                  <c:v>-1.4811706496402619E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-4.1093825711868698E-4</c:v>
+                  <c:v>-1.39673228841275E-3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-1.3200663961470129E-3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.8323860866948962E-4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-1.650638529099524E-3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-7.7730178600177169E-4</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.4698485978879029E-4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-1.1374950408935549E-3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7.8896520426496863E-4</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-1.0729408822953701E-3</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.5233268388546998E-4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.4462700821459288E-4</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-1.187992093036883E-4</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.6878127644304189E-4</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-1.1765670496970419E-3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>6.2361714662984014E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5748,7 +6156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -5805,28 +6213,28 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>6.4450860023498544</v>
+        <v>-3.3186677843332291E-2</v>
       </c>
       <c r="D2">
-        <v>0.69066405296325684</v>
+        <v>0.55288428068161011</v>
       </c>
       <c r="E2">
-        <v>0.47701683640480042</v>
+        <v>0.3056810200214386</v>
       </c>
       <c r="F2">
-        <v>9.7674643620848656E-3</v>
+        <v>7.818964309990406E-3</v>
       </c>
       <c r="G2">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>1.270020473748446E-2</v>
+        <v>4.3737016618251801E-2</v>
       </c>
       <c r="I2">
-        <v>3.2576567027717829E-3</v>
+        <v>-1.4045118587091571E-4</v>
       </c>
       <c r="J2">
         <v>50</v>
@@ -5846,28 +6254,28 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="C3">
-        <v>7.0800962448120117</v>
+        <v>2.153664112091064</v>
       </c>
       <c r="D3">
-        <v>0.79993730783462524</v>
+        <v>0.54649651050567627</v>
       </c>
       <c r="E3">
-        <v>0.63989967107772827</v>
+        <v>0.29865846037864691</v>
       </c>
       <c r="F3">
-        <v>1.131282187998295E-2</v>
+        <v>7.7286278828978539E-3</v>
       </c>
       <c r="G3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.9225925728678703E-3</v>
+        <v>3.8439903408288963E-2</v>
       </c>
       <c r="I3">
-        <v>4.8468364402651787E-3</v>
+        <v>3.8089096779003739E-4</v>
       </c>
       <c r="J3">
         <v>50</v>
@@ -5878,28 +6286,28 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="C4">
-        <v>7.4762258529663086</v>
+        <v>4.0756592750549316</v>
       </c>
       <c r="D4">
-        <v>0.93927711248397827</v>
+        <v>0.56365150213241577</v>
       </c>
       <c r="E4">
-        <v>0.88224148750305176</v>
+        <v>0.3177030086517334</v>
       </c>
       <c r="F4">
-        <v>1.328338403254747E-2</v>
+        <v>7.9712355509400368E-3</v>
       </c>
       <c r="G4">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="H4">
-        <v>4.7624204307794571E-3</v>
+        <v>2.805959619581699E-2</v>
       </c>
       <c r="I4">
-        <v>6.2064384110271931E-3</v>
+        <v>1.259137992747128E-3</v>
       </c>
       <c r="J4">
         <v>50</v>
@@ -5910,28 +6318,28 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="C5">
-        <v>7.7143468856811523</v>
+        <v>5.4786391258239746</v>
       </c>
       <c r="D5">
-        <v>1.0920455455780029</v>
+        <v>0.61697643995285034</v>
       </c>
       <c r="E5">
-        <v>1.192563414573669</v>
+        <v>0.38065990805625921</v>
       </c>
       <c r="F5">
-        <v>1.544385589659214E-2</v>
+        <v>8.7253646925091743E-3</v>
       </c>
       <c r="G5">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H5">
-        <v>2.9520320240408182E-3</v>
+        <v>1.9289026036858559E-2</v>
       </c>
       <c r="I5">
-        <v>7.3946048505604267E-3</v>
+        <v>2.1577584557235241E-3</v>
       </c>
       <c r="J5">
         <v>50</v>
@@ -5942,28 +6350,28 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="C6">
-        <v>7.8619484901428223</v>
+        <v>6.4430904388427734</v>
       </c>
       <c r="D6">
-        <v>1.2499175071716311</v>
+        <v>0.69896197319030762</v>
       </c>
       <c r="E6">
-        <v>1.562293648719788</v>
+        <v>0.48854783177375788</v>
       </c>
       <c r="F6">
-        <v>1.7676502466201779E-2</v>
+        <v>9.8848147317767143E-3</v>
       </c>
       <c r="G6">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="H6">
-        <v>2.4916362017393108E-3</v>
+        <v>1.2618923559784889E-2</v>
       </c>
       <c r="I6">
-        <v>9.5630716532468796E-3</v>
+        <v>3.0011897906661029E-3</v>
       </c>
       <c r="J6">
         <v>50</v>
@@ -5974,28 +6382,28 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="C7">
-        <v>7.9865303039550781</v>
+        <v>7.0740365982055664</v>
       </c>
       <c r="D7">
-        <v>1.428442239761353</v>
+        <v>0.79912912845611572</v>
       </c>
       <c r="E7">
-        <v>2.0404472351074219</v>
+        <v>0.63860732316970825</v>
       </c>
       <c r="F7">
-        <v>2.020122297108173E-2</v>
+        <v>1.1301392689347271E-2</v>
       </c>
       <c r="G7">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H7">
-        <v>1.7053222982212899E-3</v>
+        <v>8.0021098256111145E-3</v>
       </c>
       <c r="I7">
-        <v>1.0958137921988961E-2</v>
+        <v>4.6118269674479961E-3</v>
       </c>
       <c r="J7">
         <v>50</v>
@@ -6006,28 +6414,28 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="C8">
-        <v>8.0717964172363281</v>
+        <v>7.4741420745849609</v>
       </c>
       <c r="D8">
-        <v>1.60883629322052</v>
+        <v>0.93230825662612915</v>
       </c>
       <c r="E8">
-        <v>2.588354110717773</v>
+        <v>0.86919867992401123</v>
       </c>
       <c r="F8">
-        <v>2.2752381861209869E-2</v>
+        <v>1.318482961505651E-2</v>
       </c>
       <c r="G8">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="H8">
-        <v>1.7603683518245821E-3</v>
+        <v>4.6602725051343441E-3</v>
       </c>
       <c r="I8">
-        <v>1.3139200396835801E-2</v>
+        <v>6.0577774420380592E-3</v>
       </c>
       <c r="J8">
         <v>50</v>
@@ -6038,28 +6446,28 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="C9">
-        <v>8.1598148345947266</v>
+        <v>7.707155704498291</v>
       </c>
       <c r="D9">
-        <v>1.801475524902344</v>
+        <v>1.082629919052124</v>
       </c>
       <c r="E9">
-        <v>3.2453141212463379</v>
+        <v>1.172087550163269</v>
       </c>
       <c r="F9">
-        <v>2.5476710870862011E-2</v>
+        <v>1.5310699120163919E-2</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="H9">
-        <v>7.0329668233171105E-4</v>
+        <v>3.7211321759969E-3</v>
       </c>
       <c r="I9">
-        <v>1.275830250233412E-2</v>
+        <v>7.5320745818316936E-3</v>
       </c>
       <c r="J9">
         <v>50</v>
@@ -6070,28 +6478,28 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="C10">
-        <v>8.1949796676635742</v>
+        <v>7.8932123184204102</v>
       </c>
       <c r="D10">
-        <v>1.970591068267822</v>
+        <v>1.2444642782211299</v>
       </c>
       <c r="E10">
-        <v>3.88322925567627</v>
+        <v>1.5486912727355959</v>
       </c>
       <c r="F10">
-        <v>2.7868365868926048E-2</v>
+        <v>1.7599383369088169E-2</v>
       </c>
       <c r="G10">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="H10">
-        <v>5.4071424528956413E-4</v>
+        <v>1.9956016913056369E-3</v>
       </c>
       <c r="I10">
-        <v>1.625977456569672E-2</v>
+        <v>9.74302738904953E-3</v>
       </c>
       <c r="J10">
         <v>50</v>
@@ -6102,28 +6510,28 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="C11">
-        <v>8.222015380859375</v>
+        <v>7.9929924011230469</v>
       </c>
       <c r="D11">
-        <v>2.1670758724212651</v>
+        <v>1.42682957649231</v>
       </c>
       <c r="E11">
-        <v>4.6962180137634277</v>
+        <v>2.035842657089233</v>
       </c>
       <c r="F11">
-        <v>3.0647080391645432E-2</v>
+        <v>2.017841674387455E-2</v>
       </c>
       <c r="G11">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H11">
-        <v>2.374267642153427E-4</v>
+        <v>2.0708083175122738E-3</v>
       </c>
       <c r="I11">
-        <v>1.5251254662871361E-2</v>
+        <v>1.1423978954553601E-2</v>
       </c>
       <c r="J11">
         <v>50</v>
@@ -6134,28 +6542,28 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="C12">
-        <v>8.23388671875</v>
+        <v>8.0965328216552734</v>
       </c>
       <c r="D12">
-        <v>2.336403369903564</v>
+        <v>1.6146335601806641</v>
       </c>
       <c r="E12">
-        <v>5.4587807655334473</v>
+        <v>2.607041597366333</v>
       </c>
       <c r="F12">
-        <v>3.3041734248399728E-2</v>
+        <v>2.283436618745327E-2</v>
       </c>
       <c r="G12">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="H12">
-        <v>2.9315947904251521E-4</v>
+        <v>6.0474395286291838E-4</v>
       </c>
       <c r="I12">
-        <v>1.6766052693128589E-2</v>
+        <v>1.17067527025938E-2</v>
       </c>
       <c r="J12">
         <v>50</v>
@@ -6166,28 +6574,28 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="C13">
-        <v>8.2485446929931641</v>
+        <v>8.12677001953125</v>
       </c>
       <c r="D13">
-        <v>2.5093989372253418</v>
+        <v>1.7867230176925659</v>
       </c>
       <c r="E13">
-        <v>6.2970833778381348</v>
+        <v>3.192379236221313</v>
       </c>
       <c r="F13">
-        <v>3.5488259047269821E-2</v>
+        <v>2.526807971298695E-2</v>
       </c>
       <c r="G13">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="H13">
-        <v>-2.232666127383709E-3</v>
+        <v>1.2352180201560261E-3</v>
       </c>
       <c r="I13">
-        <v>1.5915995463728901E-2</v>
+        <v>1.4806590043008329E-2</v>
       </c>
       <c r="J13">
         <v>50</v>
@@ -6198,28 +6606,28 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="C14">
-        <v>8.1369113922119141</v>
+        <v>8.1885309219360352</v>
       </c>
       <c r="D14">
-        <v>2.663246631622314</v>
+        <v>1.9831057786941531</v>
       </c>
       <c r="E14">
-        <v>7.0928831100463867</v>
+        <v>3.932708740234375</v>
       </c>
       <c r="F14">
-        <v>3.766399621963501E-2</v>
+        <v>2.8045350685715679E-2</v>
       </c>
       <c r="G14">
-        <v>850</v>
+        <v>650</v>
       </c>
       <c r="H14">
-        <v>-1.735458383336663E-3</v>
+        <v>4.7172547783702612E-4</v>
       </c>
       <c r="I14">
-        <v>2.1937064826488491E-2</v>
+        <v>1.5090532600879669E-2</v>
       </c>
       <c r="J14">
         <v>50</v>
@@ -6230,28 +6638,28 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>850</v>
+        <v>650</v>
       </c>
       <c r="C15">
-        <v>8.0501384735107422</v>
+        <v>8.2121171951293945</v>
       </c>
       <c r="D15">
-        <v>2.8617715835571289</v>
+        <v>2.1650023460388179</v>
       </c>
       <c r="E15">
-        <v>8.1897363662719727</v>
+        <v>4.6872353553771973</v>
       </c>
       <c r="F15">
-        <v>4.0471561253070831E-2</v>
+        <v>3.0617756769061089E-2</v>
       </c>
       <c r="G15">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="H15">
-        <v>-1.3534927275031809E-3</v>
+        <v>5.6802749168127775E-4</v>
       </c>
       <c r="I15">
-        <v>1.743364334106445E-2</v>
+        <v>1.3585700653493399E-2</v>
       </c>
       <c r="J15">
         <v>50</v>
@@ -6262,28 +6670,28 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="C16">
-        <v>7.9824638366699219</v>
+        <v>8.2405185699462891</v>
       </c>
       <c r="D16">
-        <v>3.0102190971374512</v>
+        <v>2.3165750503540039</v>
       </c>
       <c r="E16">
-        <v>9.0614185333251953</v>
+        <v>5.3665204048156738</v>
       </c>
       <c r="F16">
-        <v>4.2570926249027252E-2</v>
+        <v>3.2761316746473312E-2</v>
       </c>
       <c r="G16">
-        <v>950</v>
+        <v>750</v>
       </c>
       <c r="H16">
-        <v>-2.40325927734375E-3</v>
+        <v>-8.5222243797034025E-4</v>
       </c>
       <c r="I16">
-        <v>1.5669764950871471E-2</v>
+        <v>2.0415086299180981E-2</v>
       </c>
       <c r="J16">
         <v>50</v>
@@ -6294,28 +6702,28 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>950</v>
+        <v>750</v>
       </c>
       <c r="C17">
-        <v>7.8623008728027344</v>
+        <v>8.1979074478149414</v>
       </c>
       <c r="D17">
-        <v>3.1376595497131352</v>
+        <v>2.5273058414459229</v>
       </c>
       <c r="E17">
-        <v>9.8449068069458008</v>
+        <v>6.3872747421264648</v>
       </c>
       <c r="F17">
-        <v>4.4373206794261932E-2</v>
+        <v>3.5741500556468957E-2</v>
       </c>
       <c r="G17">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H17">
-        <v>-2.6421451475471258E-3</v>
+        <v>-8.7863922817632556E-4</v>
       </c>
       <c r="I17">
-        <v>2.196176536381245E-2</v>
+        <v>1.6049737110733989E-2</v>
       </c>
       <c r="J17">
         <v>50</v>
@@ -6326,28 +6734,28 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="C18">
-        <v>7.7301936149597168</v>
+        <v>8.1539754867553711</v>
       </c>
       <c r="D18">
-        <v>3.308019876480103</v>
+        <v>2.681373119354248</v>
       </c>
       <c r="E18">
-        <v>10.942995071411129</v>
+        <v>7.1897616386413574</v>
       </c>
       <c r="F18">
-        <v>4.6782467514276498E-2</v>
+        <v>3.7920340895652771E-2</v>
       </c>
       <c r="G18">
-        <v>1050</v>
+        <v>850</v>
       </c>
       <c r="H18">
-        <v>-2.9956244397908449E-3</v>
+        <v>-1.21221540030092E-3</v>
       </c>
       <c r="I18">
-        <v>1.62501335144043E-2</v>
+        <v>1.6294583678245541E-2</v>
       </c>
       <c r="J18">
         <v>50</v>
@@ -6358,28 +6766,28 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>1050</v>
+        <v>850</v>
       </c>
       <c r="C19">
-        <v>7.5804123878479004</v>
+        <v>8.0933647155761719</v>
       </c>
       <c r="D19">
-        <v>3.4286296367645259</v>
+        <v>2.8292210102081299</v>
       </c>
       <c r="E19">
-        <v>11.755501747131349</v>
+        <v>8.004490852355957</v>
       </c>
       <c r="F19">
-        <v>4.848814383149147E-2</v>
+        <v>4.0011227130889893E-2</v>
       </c>
       <c r="G19">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="H19">
-        <v>-1.2287044664844871E-3</v>
+        <v>-2.2033595014363532E-3</v>
       </c>
       <c r="I19">
-        <v>1.218025200068951E-2</v>
+        <v>2.3055305704474449E-2</v>
       </c>
       <c r="J19">
         <v>50</v>
@@ -6390,28 +6798,28 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="C20">
-        <v>7.518977165222168</v>
+        <v>7.9831967353820801</v>
       </c>
       <c r="D20">
-        <v>3.516321182250977</v>
+        <v>3.026095867156982</v>
       </c>
       <c r="E20">
-        <v>12.36451435089111</v>
+        <v>9.1572561264038086</v>
       </c>
       <c r="F20">
-        <v>4.9728289246559143E-2</v>
+        <v>4.2795456945896149E-2</v>
       </c>
       <c r="G20">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="H20">
-        <v>-2.6163100264966488E-3</v>
+        <v>-3.214311553165317E-3</v>
       </c>
       <c r="I20">
-        <v>1.160488091409206E-2</v>
+        <v>1.651374809443951E-2</v>
       </c>
       <c r="J20">
         <v>50</v>
@@ -6422,28 +6830,28 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="C21">
-        <v>7.3881616592407227</v>
+        <v>7.8224811553955078</v>
       </c>
       <c r="D21">
-        <v>3.5978825092315669</v>
+        <v>3.159579753875732</v>
       </c>
       <c r="E21">
-        <v>12.94475841522217</v>
+        <v>9.9829435348510742</v>
       </c>
       <c r="F21">
-        <v>5.0881743431091309E-2</v>
+        <v>4.4683206826448441E-2</v>
       </c>
       <c r="G21">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H21">
-        <v>-1.2187766842544081E-3</v>
+        <v>-2.349033253267407E-3</v>
       </c>
       <c r="I21">
-        <v>1.223464962095022E-2</v>
+        <v>1.7960129305720329E-2</v>
       </c>
       <c r="J21">
         <v>50</v>
@@ -6454,28 +6862,28 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="C22">
-        <v>7.3272228240966797</v>
+        <v>7.7050294876098633</v>
       </c>
       <c r="D22">
-        <v>3.681914091110229</v>
+        <v>3.298628568649292</v>
       </c>
       <c r="E22">
-        <v>13.556490898132321</v>
+        <v>10.88094997406006</v>
       </c>
       <c r="F22">
-        <v>5.2070129662752151E-2</v>
+        <v>4.664965346455574E-2</v>
       </c>
       <c r="G22">
-        <v>1250</v>
+        <v>1050</v>
       </c>
       <c r="H22">
-        <v>-9.0398790780454874E-4</v>
+        <v>-1.940259942784905E-3</v>
       </c>
       <c r="I22">
-        <v>3.3084868919104342E-3</v>
+        <v>1.548425666987896E-2</v>
       </c>
       <c r="J22">
         <v>50</v>
@@ -6486,28 +6894,28 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>1250</v>
+        <v>1050</v>
       </c>
       <c r="C23">
-        <v>7.2820234298706046</v>
+        <v>7.6080164909362793</v>
       </c>
       <c r="D23">
-        <v>3.704310417175293</v>
+        <v>3.4139659404754639</v>
       </c>
       <c r="E23">
-        <v>13.721915245056151</v>
+        <v>11.6551628112793</v>
       </c>
       <c r="F23">
-        <v>5.238686129450798E-2</v>
+        <v>4.8280768096446991E-2</v>
       </c>
       <c r="G23">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="H23">
-        <v>-6.2022206839174032E-4</v>
+        <v>-2.0339393522590399E-3</v>
       </c>
       <c r="I23">
-        <v>3.766937181353569E-3</v>
+        <v>1.421596482396126E-2</v>
       </c>
       <c r="J23">
         <v>50</v>
@@ -6518,28 +6926,28 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="C24">
-        <v>7.2510123252868652</v>
+        <v>7.506319522857666</v>
       </c>
       <c r="D24">
-        <v>3.7296464443206792</v>
+        <v>3.5165269374847412</v>
       </c>
       <c r="E24">
-        <v>13.910262107849119</v>
+        <v>12.3659610748291</v>
       </c>
       <c r="F24">
-        <v>5.2745167165994637E-2</v>
+        <v>4.973120242357254E-2</v>
       </c>
       <c r="G24">
-        <v>1350</v>
+        <v>1150</v>
       </c>
       <c r="H24">
-        <v>-1.2161349877715111E-3</v>
+        <v>-1.833705930039287E-3</v>
       </c>
       <c r="I24">
-        <v>3.8110541645437479E-3</v>
+        <v>1.272062305361032E-2</v>
       </c>
       <c r="J24">
         <v>50</v>
@@ -6550,28 +6958,28 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>1350</v>
+        <v>1150</v>
       </c>
       <c r="C25">
-        <v>7.1902055740356454</v>
+        <v>7.4146342277526864</v>
       </c>
       <c r="D25">
-        <v>3.7551052570343022</v>
+        <v>3.6058275699615479</v>
       </c>
       <c r="E25">
-        <v>14.100814819335939</v>
+        <v>13.001992225646971</v>
       </c>
       <c r="F25">
-        <v>5.3105209022760391E-2</v>
+        <v>5.0994101911783218E-2</v>
       </c>
       <c r="G25">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="H25">
-        <v>-1.0043334914371369E-3</v>
+        <v>-1.4811706496402619E-3</v>
       </c>
       <c r="I25">
-        <v>7.9366303980350494E-3</v>
+        <v>1.0799160227179531E-2</v>
       </c>
       <c r="J25">
         <v>50</v>
@@ -6582,28 +6990,28 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="C26">
-        <v>7.139988899230957</v>
+        <v>7.3405756950378418</v>
       </c>
       <c r="D26">
-        <v>3.80757737159729</v>
+        <v>3.679938793182373</v>
       </c>
       <c r="E26">
-        <v>14.497646331787109</v>
+        <v>13.54195022583008</v>
       </c>
       <c r="F26">
-        <v>5.3847275674343109E-2</v>
+        <v>5.2042193710803993E-2</v>
       </c>
       <c r="G26">
-        <v>1450</v>
+        <v>1250</v>
       </c>
       <c r="H26">
-        <v>-4.1093825711868698E-4</v>
+        <v>-1.39673228841275E-3</v>
       </c>
       <c r="I26">
-        <v>-4.830741963814944E-4</v>
+        <v>4.0500257164239883E-3</v>
       </c>
       <c r="J26">
         <v>50</v>
@@ -6614,22 +7022,467 @@
         <v>25</v>
       </c>
       <c r="B27">
+        <v>1250</v>
+      </c>
+      <c r="C27">
+        <v>7.2707390785217294</v>
+      </c>
+      <c r="D27">
+        <v>3.7073509693145752</v>
+      </c>
+      <c r="E27">
+        <v>13.74445152282715</v>
+      </c>
+      <c r="F27">
+        <v>5.2429858595132828E-2</v>
+      </c>
+      <c r="G27">
+        <v>1300</v>
+      </c>
+      <c r="H27">
+        <v>-1.3200663961470129E-3</v>
+      </c>
+      <c r="I27">
+        <v>7.8820614144206047E-3</v>
+      </c>
+      <c r="J27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>1300</v>
+      </c>
+      <c r="C28">
+        <v>7.2047357559204102</v>
+      </c>
+      <c r="D28">
+        <v>3.7601268291473389</v>
+      </c>
+      <c r="E28">
+        <v>14.13855457305908</v>
+      </c>
+      <c r="F28">
+        <v>5.3176224231719971E-2</v>
+      </c>
+      <c r="G28">
+        <v>1350</v>
+      </c>
+      <c r="H28">
+        <v>5.8323860866948962E-4</v>
+      </c>
+      <c r="I28">
+        <v>4.0382575243711472E-3</v>
+      </c>
+      <c r="J28">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>1350</v>
+      </c>
+      <c r="C29">
+        <v>7.2338976860046387</v>
+      </c>
+      <c r="D29">
+        <v>3.7868809700012211</v>
+      </c>
+      <c r="E29">
+        <v>14.34046745300293</v>
+      </c>
+      <c r="F29">
+        <v>5.3554583340883262E-2</v>
+      </c>
+      <c r="G29">
+        <v>1400</v>
+      </c>
+      <c r="H29">
+        <v>-1.650638529099524E-3</v>
+      </c>
+      <c r="I29">
+        <v>3.5013961605727668E-3</v>
+      </c>
+      <c r="J29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>1400</v>
+      </c>
+      <c r="C30">
+        <v>7.1513657569885254</v>
+      </c>
+      <c r="D30">
+        <v>3.80992603302002</v>
+      </c>
+      <c r="E30">
+        <v>14.515537261962891</v>
+      </c>
+      <c r="F30">
+        <v>5.3880490362644202E-2</v>
+      </c>
+      <c r="G30">
         <v>1450</v>
       </c>
-      <c r="C27">
-        <v>7.1194419860839844</v>
-      </c>
-      <c r="D27">
-        <v>3.8044042587280269</v>
-      </c>
-      <c r="E27">
-        <v>14.47349262237549</v>
-      </c>
-      <c r="F27">
-        <v>5.3802400827407837E-2</v>
-      </c>
-      <c r="G27">
+      <c r="H30">
+        <v>-7.7730178600177169E-4</v>
+      </c>
+      <c r="I30">
+        <v>2.3104285355657339E-3</v>
+      </c>
+      <c r="J30">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31">
         <v>1450</v>
+      </c>
+      <c r="C31">
+        <v>7.1125006675720206</v>
+      </c>
+      <c r="D31">
+        <v>3.825056791305542</v>
+      </c>
+      <c r="E31">
+        <v>14.631058692932131</v>
+      </c>
+      <c r="F31">
+        <v>5.4094471037387848E-2</v>
+      </c>
+      <c r="G31">
+        <v>1500</v>
+      </c>
+      <c r="H31">
+        <v>3.4698485978879029E-4</v>
+      </c>
+      <c r="I31">
+        <v>1.163120265118778E-3</v>
+      </c>
+      <c r="J31">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>1500</v>
+      </c>
+      <c r="C32">
+        <v>7.129849910736084</v>
+      </c>
+      <c r="D32">
+        <v>3.8326511383056641</v>
+      </c>
+      <c r="E32">
+        <v>14.6892147064209</v>
+      </c>
+      <c r="F32">
+        <v>5.4201871156692498E-2</v>
+      </c>
+      <c r="G32">
+        <v>1550</v>
+      </c>
+      <c r="H32">
+        <v>-1.1374950408935549E-3</v>
+      </c>
+      <c r="I32">
+        <v>2.6068687438964839E-3</v>
+      </c>
+      <c r="J32">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>1550</v>
+      </c>
+      <c r="C33">
+        <v>7.0729751586914063</v>
+      </c>
+      <c r="D33">
+        <v>3.8496179580688481</v>
+      </c>
+      <c r="E33">
+        <v>14.819558143615721</v>
+      </c>
+      <c r="F33">
+        <v>5.4441820830106742E-2</v>
+      </c>
+      <c r="G33">
+        <v>1600</v>
+      </c>
+      <c r="H33">
+        <v>7.8896520426496863E-4</v>
+      </c>
+      <c r="I33">
+        <v>1.341037801466882E-3</v>
+      </c>
+      <c r="J33">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>1600</v>
+      </c>
+      <c r="C34">
+        <v>7.1124234199523926</v>
+      </c>
+      <c r="D34">
+        <v>3.8583168983459468</v>
+      </c>
+      <c r="E34">
+        <v>14.88661003112793</v>
+      </c>
+      <c r="F34">
+        <v>5.4564841091632843E-2</v>
+      </c>
+      <c r="G34">
+        <v>1650</v>
+      </c>
+      <c r="H34">
+        <v>-1.0729408822953701E-3</v>
+      </c>
+      <c r="I34">
+        <v>1.550102169858292E-4</v>
+      </c>
+      <c r="J34">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>1650</v>
+      </c>
+      <c r="C35">
+        <v>7.0587763786315918</v>
+      </c>
+      <c r="D35">
+        <v>3.8593213558197021</v>
+      </c>
+      <c r="E35">
+        <v>14.89436054229736</v>
+      </c>
+      <c r="F35">
+        <v>5.4579045623540878E-2</v>
+      </c>
+      <c r="G35">
+        <v>1700</v>
+      </c>
+      <c r="H35">
+        <v>2.5233268388546998E-4</v>
+      </c>
+      <c r="I35">
+        <v>3.304977435618639E-3</v>
+      </c>
+      <c r="J35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>1700</v>
+      </c>
+      <c r="C36">
+        <v>7.0713930130004883</v>
+      </c>
+      <c r="D36">
+        <v>3.8806712627410889</v>
+      </c>
+      <c r="E36">
+        <v>15.059609413146971</v>
+      </c>
+      <c r="F36">
+        <v>5.4880980402231223E-2</v>
+      </c>
+      <c r="G36">
+        <v>1750</v>
+      </c>
+      <c r="H36">
+        <v>2.4462700821459288E-4</v>
+      </c>
+      <c r="I36">
+        <v>-2.330856397747993E-3</v>
+      </c>
+      <c r="J36">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>1750</v>
+      </c>
+      <c r="C37">
+        <v>7.0836243629455566</v>
+      </c>
+      <c r="D37">
+        <v>3.865626335144043</v>
+      </c>
+      <c r="E37">
+        <v>14.94306659698486</v>
+      </c>
+      <c r="F37">
+        <v>5.4668210446834557E-2</v>
+      </c>
+      <c r="G37">
+        <v>1800</v>
+      </c>
+      <c r="H37">
+        <v>-1.187992093036883E-4</v>
+      </c>
+      <c r="I37">
+        <v>2.4044991005212069E-3</v>
+      </c>
+      <c r="J37">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>1800</v>
+      </c>
+      <c r="C38">
+        <v>7.0776844024658203</v>
+      </c>
+      <c r="D38">
+        <v>3.881145715713501</v>
+      </c>
+      <c r="E38">
+        <v>15.063291549682621</v>
+      </c>
+      <c r="F38">
+        <v>5.4887689650058753E-2</v>
+      </c>
+      <c r="G38">
+        <v>1850</v>
+      </c>
+      <c r="H38">
+        <v>1.6878127644304189E-4</v>
+      </c>
+      <c r="I38">
+        <v>-1.9380188314244149E-3</v>
+      </c>
+      <c r="J38">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>1850</v>
+      </c>
+      <c r="C39">
+        <v>7.0861234664916992</v>
+      </c>
+      <c r="D39">
+        <v>3.86864185333252</v>
+      </c>
+      <c r="E39">
+        <v>14.966390609741209</v>
+      </c>
+      <c r="F39">
+        <v>5.4710857570171363E-2</v>
+      </c>
+      <c r="G39">
+        <v>1900</v>
+      </c>
+      <c r="H39">
+        <v>-1.1765670496970419E-3</v>
+      </c>
+      <c r="I39">
+        <v>2.488365164026618E-3</v>
+      </c>
+      <c r="J39">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>1900</v>
+      </c>
+      <c r="C40">
+        <v>7.0272951126098633</v>
+      </c>
+      <c r="D40">
+        <v>3.884689092636108</v>
+      </c>
+      <c r="E40">
+        <v>15.0908088684082</v>
+      </c>
+      <c r="F40">
+        <v>5.4937798529863358E-2</v>
+      </c>
+      <c r="G40">
+        <v>1950</v>
+      </c>
+      <c r="H40">
+        <v>6.2361714662984014E-4</v>
+      </c>
+      <c r="I40">
+        <v>2.5373650714755058E-3</v>
+      </c>
+      <c r="J40">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>1950</v>
+      </c>
+      <c r="C41">
+        <v>7.0584759712219238</v>
+      </c>
+      <c r="D41">
+        <v>3.9009840488433838</v>
+      </c>
+      <c r="E41">
+        <v>15.217677116394039</v>
+      </c>
+      <c r="F41">
+        <v>5.5168244987726212E-2</v>
       </c>
     </row>
   </sheetData>
